--- a/testDjangosite/media/excel_files/listregion/listregion_field_desc527.xlsx
+++ b/testDjangosite/media/excel_files/listregion/listregion_field_desc527.xlsx
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -133,6 +133,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1013,7 +1016,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>560000</v>
+        <v>700</v>
       </c>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
@@ -1027,7 +1030,7 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n">
-        <v>6460000</v>
+        <v>8075</v>
       </c>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
@@ -1347,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1475,7 +1478,11 @@
           <t>Площадь участка</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr"/>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -1493,6 +1500,11 @@
       <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Целевое назначение лесов</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Эксплуатационные</t>
         </is>
       </c>
     </row>
@@ -1503,6 +1515,11 @@
           <t>Категория защитных лесов</t>
         </is>
       </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>леса, расположенные на особо охраняемых природных территориях;</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr"/>
@@ -1528,6 +1545,11 @@
           <t>Участок находится в аренде (постоянном бессрочном пользовании)</t>
         </is>
       </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -1540,6 +1562,11 @@
           <t>Категория земель лесного фонда, на которой восстановлено лесное насаждение</t>
         </is>
       </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>вырубка</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -1552,6 +1579,11 @@
           <t>Способ лесовосстановления</t>
         </is>
       </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>искусственное лесовосстановление</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -1579,6 +1611,11 @@
       <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Тип лесорастительных условий</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>В5</t>
         </is>
       </c>
     </row>
@@ -1658,149 +1695,198 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Результаты натурного обследования</t>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
+          <t>Результаты натурного обследования</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
           <t>Закладка пробных площадей</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Площадь 1 пробной площади</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>кв. м</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>9.</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Количество пробных площадей</t>
+          <t>Площадь 1 пробной площади</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кв. м</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Количество пробных площадей</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
           <t>10.</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Координаты пробных площадей участка (в десятичных градусах с округлением до шестого знака):</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>№ пробной
 площади</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Широта</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Долгота</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="25" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>11.11111</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>22.22222</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Характеристика молодняка:</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>11.</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Породный состав</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>12,  хозяйство, полнота (сомкнутость крон) , запас  м³/га</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+    <row r="43" ht="54" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Коэффициент
 состава</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Порода</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Возраст,
 лет</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Средняя
 высота, м</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Средний
 диаметр, см</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>Количество учтенных
 древесных растений,
@@ -1809,160 +1895,224 @@
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Актинидия острая</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>3230000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>АБРИКОС сибирский</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>280000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Заключение</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>12.</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Участок критериям и требованиям к молоднякам, площади которых подлежат отнесению к землям, на которых расположены леса, указанным в Правилах лесовосстановления, утвержденных приказом Минприроды России от 1014 (с изменениями) или лесохозяйственном регламенте лесничества:</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Молодняк не соответствует Правилам лесовосстановления по средней высоте деревьев главных пород</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr"/>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Участок хозяйству при отнесении к землям, на которых расположены леса, указанному в Акте отнесения земель, предназначенных для лесовосстановления, к землям, на которых расположены леса, от  № , утвержденному </t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>13.</t>
-        </is>
-      </c>
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>В случае несоответствия участка критериям и требованиям к молоднякам, площади которых подлежат отнесению к землям, на которых расположены леса, указанным в Правилах лесовосстановления, утвержденных приказом Минприроды России от 1014 (с изменениями) или лесохозяйственном регламенте лесничества, указать категорию земель лесного фонда, к которой относится участок</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>14.</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>В случае отсутствия критериев для перевода в Правилах лесовосстановления необходимо внести реквизиты лесохозяйственного регламента:</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Участок критериям и требованиям к молоднякам, площади которых подлежат отнесению к землям, на которых расположены леса, указанным в Правилах лесовосстановления, утвержденных приказом Минприроды России от 1014 (с изменениями) или лесохозяйственном регламенте лесничества:</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Молодняк не соответствует Правилам лесовосстановления по средней высоте деревьев главных пород</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr"/>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Участок хозяйству при отнесении к землям, на которых расположены леса, указанному в Акте отнесения земель, предназначенных для лесовосстановления, к землям, на которых расположены леса, от  № , утвержденному </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>В случае несоответствия участка критериям и требованиям к молоднякам, площади которых подлежат отнесению к землям, на которых расположены леса, указанным в Правилах лесовосстановления, утвержденных приказом Минприроды России от 1014 (с изменениями) или лесохозяйственном регламенте лесничества, указать категорию земель лесного фонда, к которой относится участок</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>вырубка</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>14.</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>В случае отсутствия критериев для перевода в Правилах лесовосстановления необходимо внести реквизиты лесохозяйственного регламента:</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
           <t>15.</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Рекомендации</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>Отсутствует</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>16.</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Особенности участка</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>Обследование провел</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>В присутствии</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>Дата и время натурного обследования</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>2025-12-18T00:00:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>с</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>17:50</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
+          <t>Обследование провел</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>В присутствии</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Дата и время натурного обследования</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-18T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>с</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
           <t>по</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>17:51</t>
         </is>
@@ -1971,21 +2121,21 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="C49:G49"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A31:G31"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C54:G54"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="C41:G41"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C52:G52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
